--- a/docs/validation/V16_Left_Censored_Cohort_Labelled.xlsx
+++ b/docs/validation/V16_Left_Censored_Cohort_Labelled.xlsx
@@ -660,7 +660,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F120"/>
+  <dimension ref="A1:F122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="B39" s="14" t="inlineStr">
         <is>
-          <t>Double-click the R3 file — the R3 file. Power BI Desktop opens it and shows the first report page.</t>
+          <t>Double-click the R3 file — R3_Assortment_Supplier.pbip. Power BI Desktop opens it and shows the first report page.</t>
         </is>
       </c>
     </row>
@@ -1217,236 +1217,250 @@
       </c>
       <c r="F51" s="8" t="n"/>
     </row>
-    <row r="52" ht="28" customHeight="1">
+    <row r="52" ht="43" customHeight="1">
       <c r="B52" s="10" t="inlineStr">
         <is>
+          <t>8.2</t>
+        </is>
+      </c>
+      <c r="C52" s="10" t="inlineStr">
+        <is>
+          <t>Cohort Size KPI</t>
+        </is>
+      </c>
+      <c r="D52" s="10" t="inlineStr">
+        <is>
+          <t>Filter excludes 2017, or caveat text on the page — document 15 §7.2 flags every visual on this page</t>
+        </is>
+      </c>
+      <c r="E52" s="10" t="n"/>
+      <c r="F52" s="8" t="n"/>
+    </row>
+    <row r="53" ht="28" customHeight="1">
+      <c r="B53" s="10" t="inlineStr">
+        <is>
           <t>8.3</t>
         </is>
       </c>
-      <c r="C52" s="10" t="inlineStr">
+      <c r="C53" s="10" t="inlineStr">
         <is>
           <t>12-Month Survival KPI</t>
         </is>
       </c>
-      <c r="D52" s="10" t="inlineStr">
+      <c r="D53" s="10" t="inlineStr">
         <is>
           <t>Filter excludes 2017, or caveat text on the page</t>
         </is>
       </c>
-      <c r="E52" s="10" t="inlineStr"/>
-      <c r="F52" s="18" t="n"/>
-    </row>
-    <row r="53" ht="28" customHeight="1">
-      <c r="B53" s="12" t="inlineStr">
+      <c r="E53" s="10" t="inlineStr"/>
+      <c r="F53" s="8" t="n"/>
+    </row>
+    <row r="54" ht="28" customHeight="1">
+      <c r="B54" s="12" t="inlineStr">
         <is>
           <t>8.4</t>
         </is>
       </c>
-      <c r="C53" s="12" t="inlineStr">
+      <c r="C54" s="12" t="inlineStr">
         <is>
           <t>24-Month Survival KPI</t>
         </is>
       </c>
-      <c r="D53" s="12" t="inlineStr">
+      <c r="D54" s="12" t="inlineStr">
         <is>
           <t>Filter excludes 2017, or caveat text on the page</t>
         </is>
       </c>
-      <c r="E53" s="12" t="inlineStr"/>
-      <c r="F53" s="18" t="n"/>
-    </row>
-    <row r="54" ht="28" customHeight="1">
-      <c r="B54" s="10" t="inlineStr">
+      <c r="E54" s="12" t="inlineStr"/>
+      <c r="F54" s="8" t="n"/>
+    </row>
+    <row r="55" ht="56.5" customHeight="1">
+      <c r="B55" s="12" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="C55" s="12" t="inlineStr">
+        <is>
+          <t>Tenure Distribution</t>
+        </is>
+      </c>
+      <c r="D55" s="12" t="inlineStr">
+        <is>
+          <t>Filter excludes 2017, or caveat text on the page — 2017 items’ months active start at the data start, not at launch</t>
+        </is>
+      </c>
+      <c r="E55" s="12" t="n"/>
+      <c r="F55" s="8" t="n"/>
+    </row>
+    <row r="56" ht="28" customHeight="1">
+      <c r="B56" s="10" t="inlineStr">
         <is>
           <t>8.6</t>
         </is>
       </c>
-      <c r="C54" s="10" t="inlineStr">
+      <c r="C56" s="10" t="inlineStr">
         <is>
           <t>Survival by Cohort</t>
         </is>
       </c>
-      <c r="D54" s="10" t="inlineStr">
+      <c r="D56" s="10" t="inlineStr">
         <is>
           <t>2017 excluded from the axis, or caveat text</t>
         </is>
       </c>
-      <c r="E54" s="10" t="inlineStr"/>
-      <c r="F54" s="18" t="n"/>
-    </row>
-    <row r="55" ht="16" customHeight="1">
-      <c r="B55" s="12" t="inlineStr">
+      <c r="E56" s="10" t="inlineStr"/>
+      <c r="F56" s="8" t="n"/>
+    </row>
+    <row r="57" ht="16" customHeight="1">
+      <c r="B57" s="12" t="inlineStr">
         <is>
           <t>8.7</t>
         </is>
       </c>
-      <c r="C55" s="12" t="inlineStr">
+      <c r="C57" s="12" t="inlineStr">
         <is>
           <t>Survival Grid</t>
         </is>
       </c>
-      <c r="D55" s="12" t="inlineStr">
+      <c r="D57" s="12" t="inlineStr">
         <is>
           <t>2017 row excluded, or caveat text</t>
         </is>
       </c>
-      <c r="E55" s="12" t="inlineStr"/>
-      <c r="F55" s="18" t="n"/>
-    </row>
-    <row r="56" ht="42" customHeight="1">
-      <c r="B56" s="10" t="inlineStr">
+      <c r="E57" s="12" t="inlineStr"/>
+      <c r="F57" s="8" t="n"/>
+    </row>
+    <row r="58" ht="42" customHeight="1">
+      <c r="B58" s="10" t="inlineStr">
         <is>
           <t>8.8</t>
         </is>
       </c>
-      <c r="C56" s="10" t="inlineStr">
+      <c r="C58" s="10" t="inlineStr">
         <is>
           <t>Size vs Success</t>
         </is>
       </c>
-      <c r="D56" s="10" t="inlineStr">
+      <c r="D58" s="10" t="inlineStr">
         <is>
           <t>2017 point coloured #C8860A and caveat text box at the spec position</t>
         </is>
       </c>
-      <c r="E56" s="10" t="inlineStr"/>
-      <c r="F56" s="18" t="n"/>
-    </row>
-    <row r="57" ht="16" customHeight="1">
-      <c r="B57" s="19" t="inlineStr">
-        <is>
-          <t>The survival visuals on R3 Page 2, from document 15.</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="8" customHeight="1"/>
-    <row r="59" ht="22" customHeight="1">
-      <c r="A59" s="5" t="inlineStr">
+      <c r="E58" s="10" t="inlineStr"/>
+      <c r="F58" s="8" t="n"/>
+    </row>
+    <row r="59" ht="16" customHeight="1">
+      <c r="B59" s="19" t="inlineStr">
+        <is>
+          <t>Every visual on R3 Page 2 from document 15 — §7.2 says to flag 2017 on all of them.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="8" customHeight="1"/>
+    <row r="61" ht="22" customHeight="1">
+      <c r="A61" s="5" t="inlineStr">
         <is>
           <t>5. DECIDE: PASS OR FAIL</t>
         </is>
       </c>
     </row>
-    <row r="60" ht="16" customHeight="1">
-      <c r="B60" s="14" t="inlineStr">
+    <row r="62" ht="16" customHeight="1">
+      <c r="B62" s="14" t="inlineStr">
         <is>
           <t>Decide against the pass criterion only — it is repeated in At a Glance. Find the row below that matches what you saw.</t>
         </is>
       </c>
     </row>
-    <row r="61" ht="20" customHeight="1">
-      <c r="B61" s="6" t="inlineStr">
+    <row r="63" ht="20" customHeight="1">
+      <c r="B63" s="6" t="inlineStr">
         <is>
           <t>If you see</t>
         </is>
       </c>
-      <c r="C61" s="6" t="inlineStr">
+      <c r="C63" s="6" t="inlineStr">
         <is>
           <t>It means</t>
         </is>
       </c>
-      <c r="D61" s="8" t="n"/>
-      <c r="E61" s="6" t="inlineStr">
+      <c r="D63" s="8" t="n"/>
+      <c r="E63" s="6" t="inlineStr">
         <is>
           <t>Result</t>
         </is>
       </c>
-      <c r="F61" s="8" t="n"/>
-    </row>
-    <row r="62" ht="16" customHeight="1">
-      <c r="B62" s="10" t="inlineStr">
+      <c r="F63" s="8" t="n"/>
+    </row>
+    <row r="64" ht="16" customHeight="1">
+      <c r="B64" s="10" t="inlineStr">
         <is>
           <t>Every row Pass</t>
         </is>
       </c>
-      <c r="C62" s="10" t="inlineStr">
+      <c r="C64" s="10" t="inlineStr">
         <is>
           <t>No reader can compare 2017 unwarned</t>
         </is>
       </c>
-      <c r="D62" s="8" t="n"/>
-      <c r="E62" s="10" t="inlineStr">
+      <c r="D64" s="8" t="n"/>
+      <c r="E64" s="10" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="F62" s="8" t="n"/>
-    </row>
-    <row r="63" ht="16" customHeight="1">
-      <c r="B63" s="12" t="inlineStr">
+      <c r="F64" s="8" t="n"/>
+    </row>
+    <row r="65" ht="16" customHeight="1">
+      <c r="B65" s="12" t="inlineStr">
         <is>
           <t>Any row fails</t>
         </is>
       </c>
-      <c r="C63" s="12" t="inlineStr">
+      <c r="C65" s="12" t="inlineStr">
         <is>
           <t>2017 appears as an ordinary cohort</t>
         </is>
       </c>
-      <c r="D63" s="8" t="n"/>
-      <c r="E63" s="12" t="inlineStr">
+      <c r="D65" s="8" t="n"/>
+      <c r="E65" s="12" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
       </c>
-      <c r="F63" s="8" t="n"/>
-    </row>
-    <row r="64" ht="8" customHeight="1"/>
-    <row r="65" ht="22" customHeight="1">
-      <c r="A65" s="5" t="inlineStr">
+      <c r="F65" s="8" t="n"/>
+    </row>
+    <row r="66" ht="8" customHeight="1"/>
+    <row r="67" ht="22" customHeight="1">
+      <c r="A67" s="5" t="inlineStr">
         <is>
           <t>6. RECORD THE RESULT</t>
         </is>
       </c>
     </row>
-    <row r="66" ht="20" customHeight="1">
-      <c r="B66" s="13" t="inlineStr">
+    <row r="68" ht="20" customHeight="1">
+      <c r="B68" s="13" t="inlineStr">
         <is>
           <t>6.1 In document 22</t>
         </is>
       </c>
     </row>
-    <row r="67" ht="16" customHeight="1">
-      <c r="A67" s="16" t="n">
+    <row r="69" ht="16" customHeight="1">
+      <c r="A69" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="B67" s="14" t="inlineStr">
+      <c r="B69" s="14" t="inlineStr">
         <is>
           <t>Open X:\retail-sector-health\docs\22_Validation_Results.xlsx in Excel.</t>
         </is>
       </c>
     </row>
-    <row r="68" ht="16" customHeight="1">
-      <c r="A68" s="16" t="n">
+    <row r="70" ht="16" customHeight="1">
+      <c r="A70" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="B68" s="14" t="inlineStr">
+      <c r="B70" s="14" t="inlineStr">
         <is>
           <t>Select the Run Summary tab. Find the row for this run.</t>
-        </is>
-      </c>
-    </row>
-    <row r="69" ht="29" customHeight="1">
-      <c r="B69" s="17" t="inlineStr">
-        <is>
-          <t>◦</t>
-        </is>
-      </c>
-      <c r="C69" s="14" t="inlineStr">
-        <is>
-          <t>If you are checking during the first build, the run is Run 1. If Run 1 is not there yet, type Run 1 in the first empty Run ID cell.</t>
-        </is>
-      </c>
-    </row>
-    <row r="70" ht="29" customHeight="1">
-      <c r="B70" s="17" t="inlineStr">
-        <is>
-          <t>◦</t>
-        </is>
-      </c>
-      <c r="C70" s="14" t="inlineStr">
-        <is>
-          <t>Fill in Date, Trigger (choose from the drop-down: Initial build for the first build), Model / commit reference and Run by.</t>
         </is>
       </c>
     </row>
@@ -1458,71 +1472,71 @@
       </c>
       <c r="C71" s="14" t="inlineStr">
         <is>
+          <t>If you are checking during the first build, the run is Run 1. If Run 1 is not there yet, type Run 1 in the first empty Run ID cell.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="29" customHeight="1">
+      <c r="B72" s="17" t="inlineStr">
+        <is>
+          <t>◦</t>
+        </is>
+      </c>
+      <c r="C72" s="14" t="inlineStr">
+        <is>
+          <t>Fill in Date, Trigger (choose from the drop-down: Initial build for the first build), Model / commit reference and Run by.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="29" customHeight="1">
+      <c r="B73" s="17" t="inlineStr">
+        <is>
+          <t>◦</t>
+        </is>
+      </c>
+      <c r="C73" s="14" t="inlineStr">
+        <is>
           <t>For Model / commit reference, open PowerShell, run the command below, and type the seven characters it prints.</t>
         </is>
       </c>
     </row>
-    <row r="72" ht="16" customHeight="1">
-      <c r="B72" s="17" t="inlineStr">
+    <row r="74" ht="16" customHeight="1">
+      <c r="B74" s="17" t="inlineStr">
         <is>
           <t>◦</t>
         </is>
       </c>
-      <c r="C72" s="14" t="inlineStr">
+      <c r="C74" s="14" t="inlineStr">
         <is>
           <t>Do not type in the columns from Checks recorded to Outcome. They are formulas and fill themselves in.</t>
         </is>
       </c>
     </row>
-    <row r="73" ht="15" customHeight="1">
-      <c r="B73" s="20" t="inlineStr">
+    <row r="75" ht="15" customHeight="1">
+      <c r="B75" s="20" t="inlineStr">
         <is>
           <t>git -C X:\retail-sector-health log -1 --format=%h</t>
         </is>
       </c>
     </row>
-    <row r="74" ht="6" customHeight="1"/>
-    <row r="75" ht="16" customHeight="1">
-      <c r="A75" s="16" t="n">
+    <row r="76" ht="6" customHeight="1"/>
+    <row r="77" ht="16" customHeight="1">
+      <c r="A77" s="16" t="n">
         <v>3</v>
       </c>
-      <c r="B75" s="14" t="inlineStr">
+      <c r="B77" s="14" t="inlineStr">
         <is>
           <t>Select the Check Results tab. Find the row whose Run ID is this run and whose # is 16.</t>
         </is>
       </c>
     </row>
-    <row r="76" ht="16" customHeight="1">
-      <c r="A76" s="16" t="n">
+    <row r="78" ht="16" customHeight="1">
+      <c r="A78" s="16" t="n">
         <v>4</v>
       </c>
-      <c r="B76" s="14" t="inlineStr">
+      <c r="B78" s="14" t="inlineStr">
         <is>
           <t>Fill in four cells on that row:</t>
-        </is>
-      </c>
-    </row>
-    <row r="77" ht="16" customHeight="1">
-      <c r="B77" s="17" t="inlineStr">
-        <is>
-          <t>◦</t>
-        </is>
-      </c>
-      <c r="C77" s="14" t="inlineStr">
-        <is>
-          <t>Result: choose Pass, Fail or N/A from the drop-down.</t>
-        </is>
-      </c>
-    </row>
-    <row r="78" ht="16" customHeight="1">
-      <c r="B78" s="17" t="inlineStr">
-        <is>
-          <t>◦</t>
-        </is>
-      </c>
-      <c r="C78" s="14" t="inlineStr">
-        <is>
-          <t>Observed value / evidence: the numbers you saw — see the examples below. Never just ‘ok’.</t>
         </is>
       </c>
     </row>
@@ -1534,7 +1548,7 @@
       </c>
       <c r="C79" s="14" t="inlineStr">
         <is>
-          <t>Checked by: your name or initials.</t>
+          <t>Result: choose Pass, Fail or N/A from the drop-down.</t>
         </is>
       </c>
     </row>
@@ -1546,59 +1560,53 @@
       </c>
       <c r="C80" s="14" t="inlineStr">
         <is>
+          <t>Observed value / evidence: the numbers you saw — see the examples below. Never just ‘ok’.</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="16" customHeight="1">
+      <c r="B81" s="17" t="inlineStr">
+        <is>
+          <t>◦</t>
+        </is>
+      </c>
+      <c r="C81" s="14" t="inlineStr">
+        <is>
+          <t>Checked by: your name or initials.</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="16" customHeight="1">
+      <c r="B82" s="17" t="inlineStr">
+        <is>
+          <t>◦</t>
+        </is>
+      </c>
+      <c r="C82" s="14" t="inlineStr">
+        <is>
           <t>Date checked: today’s date.</t>
         </is>
       </c>
     </row>
-    <row r="81" ht="16" customHeight="1">
-      <c r="A81" s="16" t="n">
+    <row r="83" ht="16" customHeight="1">
+      <c r="A83" s="16" t="n">
         <v>5</v>
       </c>
-      <c r="B81" s="14" t="inlineStr">
+      <c r="B83" s="14" t="inlineStr">
         <is>
           <t>Save the workbook. Go back to Run Summary: Checks recorded has gone up by one.</t>
         </is>
       </c>
     </row>
-    <row r="82" ht="20" customHeight="1">
-      <c r="B82" s="6" t="inlineStr">
+    <row r="84" ht="20" customHeight="1">
+      <c r="B84" s="6" t="inlineStr">
         <is>
           <t>Situation</t>
         </is>
       </c>
-      <c r="C82" s="6" t="inlineStr">
+      <c r="C84" s="6" t="inlineStr">
         <is>
           <t>Write this in Observed value / evidence</t>
-        </is>
-      </c>
-      <c r="D82" s="7" t="n"/>
-      <c r="E82" s="7" t="n"/>
-      <c r="F82" s="8" t="n"/>
-    </row>
-    <row r="83" ht="16" customHeight="1">
-      <c r="B83" s="10" t="inlineStr">
-        <is>
-          <t>Example of a pass</t>
-        </is>
-      </c>
-      <c r="C83" s="10" t="inlineStr">
-        <is>
-          <t>R3 P2: page filter CohortYear ≠ 2017 on 8.3, 8.4, 8.6, 8.7 · 8.8 keeps 2017 in #C8860A with caveat text box</t>
-        </is>
-      </c>
-      <c r="D83" s="7" t="n"/>
-      <c r="E83" s="7" t="n"/>
-      <c r="F83" s="8" t="n"/>
-    </row>
-    <row r="84" ht="28" customHeight="1">
-      <c r="B84" s="12" t="inlineStr">
-        <is>
-          <t>Example of another result</t>
-        </is>
-      </c>
-      <c r="C84" s="12" t="inlineStr">
-        <is>
-          <t>Fail: 8.6 shows 2017 with no caveat</t>
         </is>
       </c>
       <c r="D84" s="7" t="n"/>
@@ -1606,185 +1614,191 @@
       <c r="F84" s="8" t="n"/>
     </row>
     <row r="85" ht="16" customHeight="1">
-      <c r="B85" s="19" t="inlineStr">
+      <c r="B85" s="10" t="inlineStr">
+        <is>
+          <t>Example of a pass</t>
+        </is>
+      </c>
+      <c r="C85" s="10" t="inlineStr">
+        <is>
+          <t>R3 P2: page filter CohortYear ≠ 2017 on 8.2 to 8.7 · 8.8 keeps 2017 in #C8860A with caveat text box</t>
+        </is>
+      </c>
+      <c r="D85" s="7" t="n"/>
+      <c r="E85" s="7" t="n"/>
+      <c r="F85" s="8" t="n"/>
+    </row>
+    <row r="86" ht="28" customHeight="1">
+      <c r="B86" s="12" t="inlineStr">
+        <is>
+          <t>Example of another result</t>
+        </is>
+      </c>
+      <c r="C86" s="12" t="inlineStr">
+        <is>
+          <t>Fail: 8.6 shows 2017 with no caveat</t>
+        </is>
+      </c>
+      <c r="D86" s="7" t="n"/>
+      <c r="E86" s="7" t="n"/>
+      <c r="F86" s="8" t="n"/>
+    </row>
+    <row r="87" ht="16" customHeight="1">
+      <c r="B87" s="19" t="inlineStr">
         <is>
           <t>Examples show the wording and level of detail to aim for. The numbers in them are illustrations, not expected values.</t>
         </is>
       </c>
     </row>
-    <row r="86" ht="20" customHeight="1">
-      <c r="B86" s="13" t="inlineStr">
+    <row r="88" ht="20" customHeight="1">
+      <c r="B88" s="13" t="inlineStr">
         <is>
           <t>6.2 In document 26</t>
         </is>
       </c>
     </row>
-    <row r="87" ht="16" customHeight="1">
-      <c r="A87" s="16" t="n">
+    <row r="89" ht="16" customHeight="1">
+      <c r="A89" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="B87" s="14" t="inlineStr">
+      <c r="B89" s="14" t="inlineStr">
         <is>
           <t>Open X:\retail-sector-health\docs\26_Validation_Timing_Checklist.xlsx and select the Build Checklist tab.</t>
         </is>
       </c>
     </row>
-    <row r="88" ht="29" customHeight="1">
-      <c r="A88" s="16" t="n">
+    <row r="90" ht="29" customHeight="1">
+      <c r="A90" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="B88" s="14" t="inlineStr">
+      <c r="B90" s="14" t="inlineStr">
         <is>
           <t>Find the row with the Ref shown below that matches where you are in the build. Set Result to the same result, and fill Date, Checked by and Observed value the same way.</t>
         </is>
       </c>
     </row>
-    <row r="89" ht="20" customHeight="1">
-      <c r="B89" s="6" t="inlineStr">
+    <row r="91" ht="20" customHeight="1">
+      <c r="B91" s="6" t="inlineStr">
         <is>
           <t>Ref in doc 26</t>
         </is>
       </c>
-      <c r="C89" s="6" t="inlineStr">
+      <c r="C91" s="6" t="inlineStr">
         <is>
           <t>When it applies</t>
-        </is>
-      </c>
-      <c r="D89" s="7" t="n"/>
-      <c r="E89" s="7" t="n"/>
-      <c r="F89" s="8" t="n"/>
-    </row>
-    <row r="90" ht="16" customHeight="1">
-      <c r="B90" s="10" t="inlineStr">
-        <is>
-          <t>G7.11</t>
-        </is>
-      </c>
-      <c r="C90" s="10" t="inlineStr">
-        <is>
-          <t>R3 Page 2 finished</t>
-        </is>
-      </c>
-      <c r="D90" s="7" t="n"/>
-      <c r="E90" s="7" t="n"/>
-      <c r="F90" s="8" t="n"/>
-    </row>
-    <row r="91" ht="16" customHeight="1">
-      <c r="B91" s="12" t="inlineStr">
-        <is>
-          <t>G8.05</t>
-        </is>
-      </c>
-      <c r="C91" s="12" t="inlineStr">
-        <is>
-          <t>R3 report pass</t>
         </is>
       </c>
       <c r="D91" s="7" t="n"/>
       <c r="E91" s="7" t="n"/>
       <c r="F91" s="8" t="n"/>
     </row>
-    <row r="92" ht="8" customHeight="1"/>
-    <row r="93" ht="22" customHeight="1">
-      <c r="A93" s="5" t="inlineStr">
+    <row r="92" ht="16" customHeight="1">
+      <c r="B92" s="10" t="inlineStr">
+        <is>
+          <t>G7.11</t>
+        </is>
+      </c>
+      <c r="C92" s="10" t="inlineStr">
+        <is>
+          <t>R3 Page 2 finished</t>
+        </is>
+      </c>
+      <c r="D92" s="7" t="n"/>
+      <c r="E92" s="7" t="n"/>
+      <c r="F92" s="8" t="n"/>
+    </row>
+    <row r="93" ht="16" customHeight="1">
+      <c r="B93" s="12" t="inlineStr">
+        <is>
+          <t>G8.05</t>
+        </is>
+      </c>
+      <c r="C93" s="12" t="inlineStr">
+        <is>
+          <t>R3 report pass</t>
+        </is>
+      </c>
+      <c r="D93" s="7" t="n"/>
+      <c r="E93" s="7" t="n"/>
+      <c r="F93" s="8" t="n"/>
+    </row>
+    <row r="94" ht="8" customHeight="1"/>
+    <row r="95" ht="22" customHeight="1">
+      <c r="A95" s="5" t="inlineStr">
         <is>
           <t>7. IF IT FAILS</t>
         </is>
       </c>
     </row>
-    <row r="94" ht="20" customHeight="1">
-      <c r="B94" s="13" t="inlineStr">
+    <row r="96" ht="20" customHeight="1">
+      <c r="B96" s="13" t="inlineStr">
         <is>
           <t>7.1 What usually causes it</t>
         </is>
       </c>
     </row>
-    <row r="95" ht="20" customHeight="1">
-      <c r="B95" s="6" t="inlineStr">
+    <row r="97" ht="20" customHeight="1">
+      <c r="B97" s="6" t="inlineStr">
         <is>
           <t>What you see</t>
         </is>
       </c>
-      <c r="C95" s="6" t="inlineStr">
+      <c r="C97" s="6" t="inlineStr">
         <is>
           <t>Likely cause</t>
         </is>
       </c>
-      <c r="D95" s="8" t="n"/>
-      <c r="E95" s="6" t="inlineStr">
+      <c r="D97" s="8" t="n"/>
+      <c r="E97" s="6" t="inlineStr">
         <is>
           <t>What to do</t>
         </is>
       </c>
-      <c r="F95" s="8" t="n"/>
-    </row>
-    <row r="96" ht="28" customHeight="1">
-      <c r="B96" s="10" t="inlineStr">
+      <c r="F97" s="8" t="n"/>
+    </row>
+    <row r="98" ht="28" customHeight="1">
+      <c r="B98" s="10" t="inlineStr">
         <is>
           <t>2017 shown without warning</t>
         </is>
       </c>
-      <c r="C96" s="10" t="inlineStr">
+      <c r="C98" s="10" t="inlineStr">
         <is>
           <t>Filter or text box missing</t>
         </is>
       </c>
-      <c r="D96" s="8" t="n"/>
-      <c r="E96" s="10" t="inlineStr">
+      <c r="D98" s="8" t="n"/>
+      <c r="E98" s="10" t="inlineStr">
         <is>
           <t>Add a page-level filter on CohortYear, or the caveat text box per document 15 spec 8.8</t>
         </is>
       </c>
-      <c r="F96" s="8" t="n"/>
-    </row>
-    <row r="97" ht="20" customHeight="1">
-      <c r="B97" s="13" t="inlineStr">
+      <c r="F98" s="8" t="n"/>
+    </row>
+    <row r="99" ht="20" customHeight="1">
+      <c r="B99" s="13" t="inlineStr">
         <is>
           <t>7.2 Record the failure</t>
         </is>
       </c>
     </row>
-    <row r="98" ht="29" customHeight="1">
-      <c r="A98" s="16" t="n">
+    <row r="100" ht="29" customHeight="1">
+      <c r="A100" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="B98" s="14" t="inlineStr">
+      <c r="B100" s="14" t="inlineStr">
         <is>
           <t>On the Check Results tab of document 22, set Result to Fail for check 16. Write the numbers you saw in Observed value. Do not change it to N/A and do not clear it.</t>
         </is>
       </c>
     </row>
-    <row r="99" ht="16" customHeight="1">
-      <c r="A99" s="16" t="n">
+    <row r="101" ht="16" customHeight="1">
+      <c r="A101" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="B99" s="14" t="inlineStr">
+      <c r="B101" s="14" t="inlineStr">
         <is>
           <t>Select the Failure Log tab and fill the first empty row:</t>
-        </is>
-      </c>
-    </row>
-    <row r="100" ht="16" customHeight="1">
-      <c r="B100" s="17" t="inlineStr">
-        <is>
-          <t>◦</t>
-        </is>
-      </c>
-      <c r="C100" s="14" t="inlineStr">
-        <is>
-          <t>Failure ID: the next number — F-001, then F-002 and so on.</t>
-        </is>
-      </c>
-    </row>
-    <row r="101" ht="16" customHeight="1">
-      <c r="B101" s="17" t="inlineStr">
-        <is>
-          <t>◦</t>
-        </is>
-      </c>
-      <c r="C101" s="14" t="inlineStr">
-        <is>
-          <t>Run ID and Check #: this run and check number.</t>
         </is>
       </c>
     </row>
@@ -1796,7 +1810,7 @@
       </c>
       <c r="C102" s="14" t="inlineStr">
         <is>
-          <t>What was observed: the same numbers.</t>
+          <t>Failure ID: the next number — F-001, then F-002 and so on.</t>
         </is>
       </c>
     </row>
@@ -1808,101 +1822,101 @@
       </c>
       <c r="C103" s="14" t="inlineStr">
         <is>
+          <t>Run ID and Check #: this run and check number.</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="16" customHeight="1">
+      <c r="B104" s="17" t="inlineStr">
+        <is>
+          <t>◦</t>
+        </is>
+      </c>
+      <c r="C104" s="14" t="inlineStr">
+        <is>
+          <t>What was observed: the same numbers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="16" customHeight="1">
+      <c r="B105" s="17" t="inlineStr">
+        <is>
+          <t>◦</t>
+        </is>
+      </c>
+      <c r="C105" s="14" t="inlineStr">
+        <is>
           <t>Root cause: what you found, or ‘not yet known’.</t>
-        </is>
-      </c>
-    </row>
-    <row r="104" ht="16" customHeight="1">
-      <c r="A104" s="16" t="n">
-        <v>3</v>
-      </c>
-      <c r="B104" s="14" t="inlineStr">
-        <is>
-          <t>Fix the cause. Then fill Fix applied, Fixed by and Date fixed. Status changes by itself to ‘Fix applied — not re-verified’.</t>
-        </is>
-      </c>
-    </row>
-    <row r="105" ht="29" customHeight="1">
-      <c r="A105" s="16" t="n">
-        <v>4</v>
-      </c>
-      <c r="B105" s="14" t="inlineStr">
-        <is>
-          <t>Run the whole procedure again as a new run — on Run Summary add Run 2 with Trigger Ad hoc and name the fix in Notes. Record the new result against Run 2.</t>
         </is>
       </c>
     </row>
     <row r="106" ht="16" customHeight="1">
       <c r="A106" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="B106" s="14" t="inlineStr">
+        <is>
+          <t>Fix the cause. Then fill Fix applied, Fixed by and Date fixed. Status changes by itself to ‘Fix applied — not re-verified’.</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="29" customHeight="1">
+      <c r="A107" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="B107" s="14" t="inlineStr">
+        <is>
+          <t>Run the whole procedure again as a new run — on Run Summary add Run 2 with Trigger Ad hoc and name the fix in Notes. Record the new result against Run 2.</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="16" customHeight="1">
+      <c r="A108" s="16" t="n">
         <v>5</v>
       </c>
-      <c r="B106" s="14" t="inlineStr">
+      <c r="B108" s="14" t="inlineStr">
         <is>
           <t>When it passes, type Run 2 in Re-verified in run on the Failure Log. Status changes to ‘Closed — re-verified’.</t>
         </is>
       </c>
     </row>
-    <row r="107" ht="8" customHeight="1"/>
-    <row r="108" ht="22" customHeight="1">
-      <c r="A108" s="5" t="inlineStr">
+    <row r="109" ht="8" customHeight="1"/>
+    <row r="110" ht="22" customHeight="1">
+      <c r="A110" s="5" t="inlineStr">
         <is>
           <t>8. WHEN TO RUN IT AGAIN</t>
         </is>
       </c>
     </row>
-    <row r="109" ht="16" customHeight="1">
-      <c r="A109" s="15" t="inlineStr">
+    <row r="111" ht="16" customHeight="1">
+      <c r="A111" s="15" t="inlineStr">
         <is>
           <t>•</t>
         </is>
       </c>
-      <c r="B109" s="14" t="inlineStr">
+      <c r="B111" s="14" t="inlineStr">
         <is>
           <t>After any R3 Page 2 visual is changed.</t>
         </is>
       </c>
     </row>
-    <row r="110" ht="16" customHeight="1">
-      <c r="A110" s="15" t="inlineStr">
+    <row r="112" ht="16" customHeight="1">
+      <c r="A112" s="15" t="inlineStr">
         <is>
           <t>•</t>
         </is>
       </c>
-      <c r="B110" s="14" t="inlineStr">
+      <c r="B112" s="14" t="inlineStr">
         <is>
           <t>At the R3 report pass.</t>
         </is>
       </c>
     </row>
-    <row r="111" ht="8" customHeight="1"/>
-    <row r="112" ht="22" customHeight="1">
-      <c r="A112" s="5" t="inlineStr">
+    <row r="113" ht="8" customHeight="1"/>
+    <row r="114" ht="22" customHeight="1">
+      <c r="A114" s="5" t="inlineStr">
         <is>
           <t>9. REFERENCES</t>
-        </is>
-      </c>
-    </row>
-    <row r="113" ht="16" customHeight="1">
-      <c r="A113" s="15" t="inlineStr">
-        <is>
-          <t>•</t>
-        </is>
-      </c>
-      <c r="B113" s="14" t="inlineStr">
-        <is>
-          <t>Document 02 §9 — the seventeen checks and their pass criteria.</t>
-        </is>
-      </c>
-    </row>
-    <row r="114" ht="16" customHeight="1">
-      <c r="A114" s="15" t="inlineStr">
-        <is>
-          <t>•</t>
-        </is>
-      </c>
-      <c r="B114" s="14" t="inlineStr">
-        <is>
-          <t>Document 22, Check Catalog tab — what this check protects against and where it runs.</t>
         </is>
       </c>
     </row>
@@ -1914,7 +1928,7 @@
       </c>
       <c r="B115" s="14" t="inlineStr">
         <is>
-          <t>Document 25 — when each check is run, and when to re-run it.</t>
+          <t>Document 02 §9 — the seventeen checks and their pass criteria.</t>
         </is>
       </c>
     </row>
@@ -1926,150 +1940,176 @@
       </c>
       <c r="B116" s="14" t="inlineStr">
         <is>
+          <t>Document 22, Check Catalog tab — what this check protects against and where it runs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="117" ht="16" customHeight="1">
+      <c r="A117" s="15" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B117" s="14" t="inlineStr">
+        <is>
+          <t>Document 25 — when each check is run, and when to re-run it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="118" ht="16" customHeight="1">
+      <c r="A118" s="15" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B118" s="14" t="inlineStr">
+        <is>
           <t>Document 26 — the gate rows this check is ticked against.</t>
         </is>
       </c>
     </row>
-    <row r="117" ht="8" customHeight="1"/>
-    <row r="118" ht="22" customHeight="1">
-      <c r="A118" s="5" t="inlineStr">
+    <row r="119" ht="8" customHeight="1"/>
+    <row r="120" ht="22" customHeight="1">
+      <c r="A120" s="5" t="inlineStr">
         <is>
           <t>10. AI ASSISTANCE DISCLOSURE</t>
         </is>
       </c>
     </row>
-    <row r="119" ht="29" customHeight="1">
-      <c r="B119" s="14" t="inlineStr">
+    <row r="121" ht="29" customHeight="1">
+      <c r="B121" s="14" t="inlineStr">
         <is>
           <t>Portions of this procedure were drafted with the assistance of a generative AI system. The author defined the project and its validation approach and reviewed all content before publication.</t>
         </is>
       </c>
     </row>
-    <row r="120" ht="43.5" customHeight="1">
-      <c r="B120" s="14" t="inlineStr">
+    <row r="122" ht="43.5" customHeight="1">
+      <c r="B122" s="14" t="inlineStr">
         <is>
           <t>The pass criterion is quoted from document 02 §9. Queries use only tables, columns and measures defined in documents 02 and 20, and the visual numbers come from the document 15 specification tables. Tool steps were checked against Microsoft Learn; where a screen label varies by version, the procedure says so.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="114">
+  <mergeCells count="116">
     <mergeCell ref="B106:F106"/>
-    <mergeCell ref="C62:D62"/>
     <mergeCell ref="B16:F16"/>
-    <mergeCell ref="E62:F62"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="A118:F118"/>
+    <mergeCell ref="C98:D98"/>
+    <mergeCell ref="B90:F90"/>
     <mergeCell ref="C72:F72"/>
+    <mergeCell ref="B122:F122"/>
+    <mergeCell ref="C81:F81"/>
     <mergeCell ref="A3:F3"/>
+    <mergeCell ref="C64:D64"/>
+    <mergeCell ref="E64:F64"/>
+    <mergeCell ref="A95:F95"/>
     <mergeCell ref="C13:F13"/>
     <mergeCell ref="E51:F51"/>
-    <mergeCell ref="C78:F78"/>
     <mergeCell ref="C63:D63"/>
     <mergeCell ref="E63:F63"/>
-    <mergeCell ref="B60:F60"/>
     <mergeCell ref="C15:F15"/>
     <mergeCell ref="C24:F24"/>
-    <mergeCell ref="C89:F89"/>
+    <mergeCell ref="E65:F65"/>
     <mergeCell ref="C79:F79"/>
+    <mergeCell ref="B116:F116"/>
     <mergeCell ref="B34:F34"/>
-    <mergeCell ref="B116:F116"/>
+    <mergeCell ref="C73:F73"/>
     <mergeCell ref="C26:F26"/>
     <mergeCell ref="B37:F37"/>
+    <mergeCell ref="B108:F108"/>
     <mergeCell ref="C10:F10"/>
+    <mergeCell ref="C93:F93"/>
+    <mergeCell ref="B118:F118"/>
     <mergeCell ref="B20:F20"/>
+    <mergeCell ref="C105:F105"/>
     <mergeCell ref="C43:F43"/>
-    <mergeCell ref="B94:F94"/>
     <mergeCell ref="E53:F53"/>
     <mergeCell ref="C27:F27"/>
     <mergeCell ref="E55:F55"/>
-    <mergeCell ref="A108:F108"/>
+    <mergeCell ref="B121:F121"/>
+    <mergeCell ref="C97:D97"/>
+    <mergeCell ref="B96:F96"/>
     <mergeCell ref="C28:F28"/>
-    <mergeCell ref="B105:F105"/>
+    <mergeCell ref="B70:F70"/>
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="C69:F69"/>
-    <mergeCell ref="C83:F83"/>
-    <mergeCell ref="B120:F120"/>
-    <mergeCell ref="B98:F98"/>
+    <mergeCell ref="B111:F111"/>
+    <mergeCell ref="C92:F92"/>
+    <mergeCell ref="B107:F107"/>
     <mergeCell ref="B17:F17"/>
+    <mergeCell ref="B88:F88"/>
     <mergeCell ref="C14:F14"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B88:F88"/>
-    <mergeCell ref="A112:F112"/>
     <mergeCell ref="B99:F99"/>
     <mergeCell ref="A30:F30"/>
-    <mergeCell ref="A59:F59"/>
+    <mergeCell ref="A114:F114"/>
     <mergeCell ref="B68:F68"/>
-    <mergeCell ref="C90:F90"/>
-    <mergeCell ref="B76:F76"/>
+    <mergeCell ref="B83:F83"/>
+    <mergeCell ref="A61:F61"/>
     <mergeCell ref="B45:F45"/>
-    <mergeCell ref="B85:F85"/>
     <mergeCell ref="C71:F71"/>
+    <mergeCell ref="E58:F58"/>
     <mergeCell ref="B75:F75"/>
-    <mergeCell ref="B109:F109"/>
+    <mergeCell ref="C8:F8"/>
     <mergeCell ref="B47:F47"/>
-    <mergeCell ref="C8:F8"/>
+    <mergeCell ref="B62:F62"/>
     <mergeCell ref="C91:F91"/>
+    <mergeCell ref="B59:F59"/>
     <mergeCell ref="C82:F82"/>
     <mergeCell ref="B31:F31"/>
     <mergeCell ref="B46:F46"/>
     <mergeCell ref="E52:F52"/>
     <mergeCell ref="C102:F102"/>
     <mergeCell ref="B39:F39"/>
-    <mergeCell ref="C77:F77"/>
-    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="C65:D65"/>
+    <mergeCell ref="C86:F86"/>
     <mergeCell ref="B87:F87"/>
-    <mergeCell ref="A93:F93"/>
     <mergeCell ref="A19:F19"/>
-    <mergeCell ref="C95:D95"/>
-    <mergeCell ref="E95:F95"/>
-    <mergeCell ref="C100:F100"/>
-    <mergeCell ref="C61:D61"/>
-    <mergeCell ref="E61:F61"/>
+    <mergeCell ref="C22:F22"/>
     <mergeCell ref="C44:F44"/>
     <mergeCell ref="C84:F84"/>
-    <mergeCell ref="C22:F22"/>
+    <mergeCell ref="E57:F57"/>
     <mergeCell ref="C80:F80"/>
     <mergeCell ref="E54:F54"/>
     <mergeCell ref="A36:F36"/>
+    <mergeCell ref="C12:F12"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="C12:F12"/>
     <mergeCell ref="C21:F21"/>
-    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="E56:F56"/>
-    <mergeCell ref="E96:F96"/>
-    <mergeCell ref="B110:F110"/>
-    <mergeCell ref="A65:F65"/>
-    <mergeCell ref="C70:F70"/>
-    <mergeCell ref="B113:F113"/>
+    <mergeCell ref="C23:F23"/>
     <mergeCell ref="C48:F48"/>
-    <mergeCell ref="C23:F23"/>
-    <mergeCell ref="B66:F66"/>
+    <mergeCell ref="B100:F100"/>
+    <mergeCell ref="E98:F98"/>
+    <mergeCell ref="A120:F120"/>
     <mergeCell ref="C7:F7"/>
     <mergeCell ref="B115:F115"/>
-    <mergeCell ref="B86:F86"/>
+    <mergeCell ref="B77:F77"/>
     <mergeCell ref="C49:F49"/>
-    <mergeCell ref="C101:F101"/>
-    <mergeCell ref="B67:F67"/>
+    <mergeCell ref="B117:F117"/>
+    <mergeCell ref="C104:F104"/>
     <mergeCell ref="A4:F4"/>
-    <mergeCell ref="C96:D96"/>
+    <mergeCell ref="B101:F101"/>
     <mergeCell ref="C42:F42"/>
-    <mergeCell ref="B119:F119"/>
+    <mergeCell ref="B41:F41"/>
+    <mergeCell ref="C74:F74"/>
+    <mergeCell ref="B69:F69"/>
     <mergeCell ref="B38:F38"/>
+    <mergeCell ref="B78:F78"/>
+    <mergeCell ref="B112:F112"/>
+    <mergeCell ref="A67:F67"/>
     <mergeCell ref="C25:F25"/>
     <mergeCell ref="C103:F103"/>
+    <mergeCell ref="C85:F85"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="C9:F9"/>
     <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B104:F104"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="A110:F110"/>
     <mergeCell ref="A6:F6"/>
+    <mergeCell ref="E97:F97"/>
     <mergeCell ref="C11:F11"/>
     <mergeCell ref="B32:F32"/>
-    <mergeCell ref="B41:F41"/>
-    <mergeCell ref="B97:F97"/>
   </mergeCells>
-  <conditionalFormatting sqref="F52:F56">
+  <conditionalFormatting sqref="F53:F58">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"Pass"</formula>
     </cfRule>
@@ -2078,7 +2118,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="F52:F56" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F52:F58" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Pass,Fail,N/A"</formula1>
     </dataValidation>
   </dataValidations>

--- a/docs/validation/V16_Left_Censored_Cohort_Labelled.xlsx
+++ b/docs/validation/V16_Left_Censored_Cohort_Labelled.xlsx
@@ -2048,8 +2048,8 @@
     <mergeCell ref="C71:F71"/>
     <mergeCell ref="E58:F58"/>
     <mergeCell ref="B75:F75"/>
+    <mergeCell ref="B47:F47"/>
     <mergeCell ref="C8:F8"/>
-    <mergeCell ref="B47:F47"/>
     <mergeCell ref="B62:F62"/>
     <mergeCell ref="C91:F91"/>
     <mergeCell ref="B59:F59"/>
@@ -2063,33 +2063,32 @@
     <mergeCell ref="C86:F86"/>
     <mergeCell ref="B87:F87"/>
     <mergeCell ref="A19:F19"/>
-    <mergeCell ref="C22:F22"/>
     <mergeCell ref="C44:F44"/>
     <mergeCell ref="C84:F84"/>
+    <mergeCell ref="C22:F22"/>
     <mergeCell ref="E57:F57"/>
     <mergeCell ref="C80:F80"/>
     <mergeCell ref="E54:F54"/>
     <mergeCell ref="A36:F36"/>
+    <mergeCell ref="A1:F1"/>
     <mergeCell ref="C12:F12"/>
-    <mergeCell ref="A1:F1"/>
     <mergeCell ref="C21:F21"/>
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="E56:F56"/>
+    <mergeCell ref="C48:F48"/>
     <mergeCell ref="C23:F23"/>
-    <mergeCell ref="C48:F48"/>
     <mergeCell ref="B100:F100"/>
     <mergeCell ref="E98:F98"/>
     <mergeCell ref="A120:F120"/>
     <mergeCell ref="C7:F7"/>
     <mergeCell ref="B115:F115"/>
     <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B117:F117"/>
     <mergeCell ref="C49:F49"/>
-    <mergeCell ref="B117:F117"/>
+    <mergeCell ref="A4:F4"/>
     <mergeCell ref="C104:F104"/>
-    <mergeCell ref="A4:F4"/>
     <mergeCell ref="B101:F101"/>
     <mergeCell ref="C42:F42"/>
-    <mergeCell ref="B41:F41"/>
     <mergeCell ref="C74:F74"/>
     <mergeCell ref="B69:F69"/>
     <mergeCell ref="B38:F38"/>
@@ -2108,6 +2107,7 @@
     <mergeCell ref="E97:F97"/>
     <mergeCell ref="C11:F11"/>
     <mergeCell ref="B32:F32"/>
+    <mergeCell ref="B41:F41"/>
   </mergeCells>
   <conditionalFormatting sqref="F53:F58">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
@@ -2119,7 +2119,7 @@
   </conditionalFormatting>
   <dataValidations count="1">
     <dataValidation sqref="F52:F58" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"Pass,Fail,N/A"</formula1>
+      <formula1>"Pass,Fail,N/A,Not run"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
